--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inbetgroup-my.sharepoint.com/personal/adriana_koleva_inbet_com/Documents/Projects/GitHub/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inbetgroup-my.sharepoint.com/personal/adriana_koleva_inbet_com/Documents/Projects/GitHub/inbet-online/careers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="11_F25DC773A252ABDACC1048DD919B7AA85ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B37D7A75-AA66-4F92-B4FB-5D5F055CFD92}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="11_F25DC773A252ABDACC1048DD919B7AA85ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22955501-665F-47F9-9E45-B720A0491CA1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Position</t>
   </si>
@@ -129,27 +129,6 @@
 Силно разбиране на динамиката на продуктите за казино и спортни залози.
 Аналитично мислене с опит в A/B тестване.
 Владее свободно английски език.</t>
-  </si>
-  <si>
-    <t>CRM Expert</t>
-  </si>
-  <si>
-    <t>The CRM Expert executes player retention campaigns and manages daily CRM operations, supporting the growth of player lifetime value across casino and sports betting segments.</t>
-  </si>
-  <si>
-    <t>Build and send targeted CRM campaigns across email, SMS, push and in-platform channels.
-Create player segments based on behaviour, product preference and activity level.
-Manage bonus and free-spin offers in the bonus engine; ensure correct tracking.
-Monitor campaign results and prepare performance reports.
-Support A/B testing initiatives.
-Maintain compliance with responsible gambling messaging requirements.</t>
-  </si>
-  <si>
-    <t>2+ years in CRM operations, preferably in online casino or sports betting.
-Hands-on with CRM or marketing automation platforms.
-Good understanding of casino game types and sportsbook operations.
-Detail-oriented; comfortable handling large datasets.
-Fluent English.</t>
   </si>
 </sst>
 </file>
@@ -512,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -639,28 +618,10 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="288.60000000000002" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="7">
-        <v>3000</v>
-      </c>
-      <c r="G6" s="7">
-        <v>3100</v>
-      </c>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
@@ -852,28 +813,23 @@
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C47" s="4"/>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C49" s="4"/>
-    </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C51" s="4"/>
-    </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C53" s="4"/>
-    </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C55" s="4"/>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B89" s="4"/>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C46" s="4"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C48" s="4"/>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C50" s="4"/>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="4"/>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C54" s="4"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B88" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inbetgroup-my.sharepoint.com/personal/adriana_koleva_inbet_com/Documents/Projects/GitHub/inbet-online/careers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="11_F25DC773A252ABDACC1048DD919B7AA85ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22955501-665F-47F9-9E45-B720A0491CA1}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="11_F25DC773A252ABDACC1048DD919B7AA85ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{040E1A86-4FF0-443E-9C44-A925BC388273}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>Position</t>
   </si>
@@ -129,6 +130,12 @@
 Силно разбиране на динамиката на продуктите за казино и спортни залози.
 Аналитично мислене с опит в A/B тестване.
 Владее свободно английски език.</t>
+  </si>
+  <si>
+    <t>Data specialist</t>
+  </si>
+  <si>
+    <t>BI</t>
   </si>
 </sst>
 </file>
@@ -619,9 +626,27 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="7">
+        <v>500</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1500</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,18 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inbetgroup-my.sharepoint.com/personal/adriana_koleva_inbet_com/Documents/Projects/GitHub/inbet-online/careers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria.atanasova\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="11_F25DC773A252ABDACC1048DD919B7AA85ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{040E1A86-4FF0-443E-9C44-A925BC388273}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B49B2FC-B16D-48CA-A989-DABA4EF5E160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11076" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Position</t>
   </si>
@@ -130,12 +129,6 @@
 Силно разбиране на динамиката на продуктите за казино и спортни залози.
 Аналитично мислене с опит в A/B тестване.
 Владее свободно английски език.</t>
-  </si>
-  <si>
-    <t>Data specialist</t>
-  </si>
-  <si>
-    <t>BI</t>
   </si>
 </sst>
 </file>
@@ -498,19 +491,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G87"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="55.77734375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="27.88671875" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" customWidth="1"/>
-    <col min="6" max="6" width="26.44140625" style="7" customWidth="1"/>
-    <col min="7" max="7" width="19.77734375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="55.7109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,7 +526,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -556,7 +549,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -579,7 +572,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -602,7 +595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>21</v>
       </c>
@@ -625,236 +618,213 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="7">
-        <v>500</v>
-      </c>
-      <c r="G6" s="7">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C46" s="4"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C48" s="4"/>
-    </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C50" s="4"/>
-    </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C52" s="4"/>
-    </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C54" s="4"/>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B88" s="4"/>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C45" s="4"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C47" s="4"/>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="4"/>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C51" s="4"/>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C53" s="4"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
